--- a/data/attendance/ECOLE_بن_يحي_BEM_فوج_2.xlsx
+++ b/data/attendance/ECOLE_بن_يحي_BEM_فوج_2.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e8525b9d-7f77-428d-9fc2-9a839e1f6481</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e5eadc9a-5af1-470a-9fe1-6980ddfc5df7</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:3adbbe8c-5da9-40e2-8188-e9bc8d1903ef</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:59723e25-e22b-448f-befe-1a84199fd4a8</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:63813e07-a4d0-441c-9c2b-2ced897389a0</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:bd734855-3890-48bc-9964-7dc0a6b35ae9</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7d7ddd88-fcfe-4e63-a678-5f559f2b0d4f</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:ac3c017a-3359-409a-83cb-1d62fdfaeb7f</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:160c536d-1dea-4ffe-83e6-c664ba742835</t>
         </r>
       </text>
@@ -149,13 +83,6 @@
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:19f05d7b-5640-4c42-acf8-a329caa9c1f2</t>
         </r>
       </text>
@@ -163,13 +90,6 @@
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0ab2978b-c270-431a-bae2-5c919efb34cf</t>
         </r>
       </text>
@@ -177,13 +97,6 @@
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:8142b498-9bf4-41b8-8ae7-5a964eb89b22</t>
         </r>
       </text>
@@ -191,13 +104,6 @@
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b153b8e4-cff3-4a83-a219-d650cd4d0505</t>
         </r>
       </text>
@@ -205,13 +111,6 @@
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:092f8781-af47-4f48-bd29-6a34cfc8876b</t>
         </r>
       </text>
@@ -219,13 +118,6 @@
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:efddb5b2-a6cc-4a02-9bc1-8a2258b2f46a</t>
         </r>
       </text>
@@ -233,13 +125,6 @@
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:02000acf-3295-4fa2-9d02-25dcb51e2ef7</t>
         </r>
       </text>
@@ -247,13 +132,6 @@
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:9bc2c4b7-354f-4acb-8565-74100613cec5</t>
         </r>
       </text>
@@ -261,13 +139,6 @@
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:2e3b3a34-1dcf-41fc-8147-03d2e4e3dc58</t>
         </r>
       </text>
@@ -275,13 +146,6 @@
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:63ee8c8d-0ba9-424f-a519-1c00bd5b8e01</t>
         </r>
       </text>
@@ -289,13 +153,6 @@
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0a1b8135-11e2-4154-85d1-769a2b8e46e5</t>
         </r>
       </text>
@@ -303,13 +160,6 @@
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1a19e1a6-ccac-4921-aaf1-05dec4ae9a1a</t>
         </r>
       </text>
@@ -317,13 +167,6 @@
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b33bbf79-0fe1-4b8f-93db-391542990c22</t>
         </r>
       </text>
@@ -331,13 +174,6 @@
     <comment ref="B27" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:081390c0-e746-40ef-9c07-58ec9bd19f2d</t>
         </r>
       </text>
@@ -345,13 +181,6 @@
     <comment ref="B28" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7b13db98-f653-40cc-8b59-f7e837345d43</t>
         </r>
       </text>
@@ -359,13 +188,6 @@
     <comment ref="B29" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:58289615-2078-46b2-9719-134cbf629d60</t>
         </r>
       </text>
@@ -373,13 +195,6 @@
     <comment ref="B30" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:24c9ea62-35f2-419a-a51d-6831b9c1de10</t>
         </r>
       </text>
@@ -387,13 +202,6 @@
     <comment ref="B31" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:be550ca7-b924-483b-9436-97d904f0bbaa</t>
         </r>
       </text>
@@ -401,13 +209,6 @@
     <comment ref="B32" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7b3d159f-f24b-4d86-9578-58d393bf269c</t>
         </r>
       </text>
@@ -415,13 +216,6 @@
     <comment ref="B33" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c1cce85f-3b48-4b64-afb0-21c6722de79f</t>
         </r>
       </text>
@@ -429,13 +223,6 @@
     <comment ref="B34" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:ac362787-4a62-406a-8234-131fef9a077f</t>
         </r>
       </text>
@@ -443,13 +230,6 @@
     <comment ref="B35" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b6d908b4-8a9c-4d79-98b4-c609d6680ef5</t>
         </r>
       </text>
@@ -457,13 +237,6 @@
     <comment ref="B36" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:559ec33b-1347-4374-84d1-082459c87534</t>
         </r>
       </text>
@@ -471,13 +244,6 @@
     <comment ref="B37" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a7848b35-4593-401a-acf7-11568dabc0ab</t>
         </r>
       </text>
@@ -485,13 +251,6 @@
     <comment ref="B38" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:f2b832ea-66a4-45ed-b472-b91739147f7a</t>
         </r>
       </text>
@@ -499,13 +258,6 @@
     <comment ref="B39" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c7c16a58-a5fc-468f-b8f2-a2d257f362bc</t>
         </r>
       </text>
@@ -515,7 +267,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
   <si>
     <t>بن يحي BEM فوج 2  |  ECOLE  |  4AM  |  بن يحيى عبد النور</t>
   </si>
@@ -529,6 +281,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -541,6 +296,9 @@
     <t>25/09/2026</t>
   </si>
   <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -676,7 +434,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -698,40 +459,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -818,7 +572,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1174,14 +928,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N39"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1199,7 +953,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1209,10 +963,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -1254,57 +1011,57 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>457</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8">
         <v>0</v>
@@ -1340,15 +1097,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>458</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
         <v>0</v>
@@ -1384,15 +1141,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>467</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -1428,15 +1185,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>468</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -1472,15 +1229,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>470</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -1516,15 +1273,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>472</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9">
         <v>0</v>
@@ -1560,15 +1317,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>474</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8">
         <v>0</v>
@@ -1604,15 +1361,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>480</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -1648,15 +1405,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>495</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="8">
         <v>0</v>
@@ -1692,15 +1449,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>776</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -1736,15 +1493,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>777</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="8">
         <v>0</v>
@@ -1780,15 +1537,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>778</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -1824,15 +1581,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>779</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8">
         <v>0</v>
@@ -1868,15 +1625,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>780</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -1912,15 +1669,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>781</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="8">
         <v>0</v>
@@ -1956,12 +1713,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>782</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" s="9">
         <v>0</v>
@@ -2000,15 +1757,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>783</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="8">
         <v>0</v>
@@ -2044,12 +1801,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>784</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" s="9">
         <v>0</v>
@@ -2088,15 +1845,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>785</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="8">
         <v>0</v>
@@ -2132,15 +1889,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>786</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="9">
         <v>0</v>
@@ -2176,15 +1933,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>787</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="8">
         <v>0</v>
@@ -2220,15 +1977,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>788</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="9">
         <v>0</v>
@@ -2264,15 +2021,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>789</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="8">
         <v>0</v>
@@ -2308,15 +2065,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>790</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="9">
         <v>0</v>
@@ -2352,15 +2109,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>791</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="8">
         <v>0</v>
@@ -2396,15 +2153,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>792</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="9">
         <v>0</v>
@@ -2440,15 +2197,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>793</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="8">
         <v>0</v>
@@ -2484,15 +2241,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>794</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="9">
         <v>0</v>
@@ -2528,15 +2285,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>795</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="8">
         <v>0</v>
@@ -2572,15 +2329,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>796</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="9">
         <v>0</v>
@@ -2616,15 +2373,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>797</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="8">
         <v>0</v>
@@ -2660,15 +2417,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>798</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="9">
         <v>0</v>
@@ -2704,15 +2461,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>799</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="8">
         <v>0</v>
@@ -2748,15 +2505,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>800</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="9">
         <v>0</v>
@@ -2792,15 +2549,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>801</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="8">
         <v>0</v>
@@ -2842,7 +2599,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2852,89 +2609,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>